--- a/testdata/BOMMigrationData.xlsx
+++ b/testdata/BOMMigrationData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Par. Item ID</t>
   </si>
@@ -65,16 +65,19 @@
     <t>IR Flag</t>
   </si>
   <si>
-    <t>GWL - BOM ITEM - 1001</t>
-  </si>
-  <si>
-    <t>GWL Automation Item for BOM</t>
+    <t>GWL-FG-10001</t>
+  </si>
+  <si>
+    <t>GWL Finished Good -10001</t>
   </si>
   <si>
     <t>GWLPROCESS-01</t>
   </si>
   <si>
-    <t>HK-TVS-RM-10001</t>
+    <t>GWL-RM-10001</t>
+  </si>
+  <si>
+    <t>GWL AUTOMATION RAW MATERIALS</t>
   </si>
   <si>
     <t>KGS</t>
@@ -738,7 +741,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1265,6 +1268,14 @@
   <sheetPr/>
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="19.3636363636364" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="6" max="6" width="14.4545454545455" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="16.3636363636364" customWidth="1"/>
+    <col min="9" max="9" width="20.5454545454545" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1330,16 +1341,16 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
